--- a/artfynd/A 18654-2025 artfynd.xlsx
+++ b/artfynd/A 18654-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484971</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484975</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484972</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484974</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,8 +1386,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484973</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 18654-2025 artfynd.xlsx
+++ b/artfynd/A 18654-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135484971</v>
       </c>
       <c r="B2" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135484975</v>
       </c>
       <c r="B3" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135484972</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135484970</v>
       </c>
       <c r="B5" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135484974</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135484973</v>
       </c>
       <c r="B7" t="n">
-        <v>92406</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18654-2025 artfynd.xlsx
+++ b/artfynd/A 18654-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135484971</v>
       </c>
       <c r="B2" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135484975</v>
       </c>
       <c r="B3" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135484972</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135484970</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135484974</v>
       </c>
       <c r="B6" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135484973</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18654-2025 artfynd.xlsx
+++ b/artfynd/A 18654-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135484971</v>
       </c>
       <c r="B2" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135484975</v>
       </c>
       <c r="B3" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135484972</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135484970</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135484974</v>
       </c>
       <c r="B6" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135484973</v>
       </c>
       <c r="B7" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18654-2025 artfynd.xlsx
+++ b/artfynd/A 18654-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135484971</v>
       </c>
       <c r="B2" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135484975</v>
       </c>
       <c r="B3" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135484972</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135484970</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135484974</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135484973</v>
       </c>
       <c r="B7" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 18654-2025 artfynd.xlsx
+++ b/artfynd/A 18654-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135484971</v>
       </c>
       <c r="B2" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135484975</v>
       </c>
       <c r="B3" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>135484972</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135484970</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>135484974</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>135484973</v>
       </c>
       <c r="B7" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
